--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run1/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run1/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7408,0.0649,0.0341,0.2032</t>
-  </si>
-  <si>
-    <t>0.0233,0.0007,0.0027,0.9865</t>
-  </si>
-  <si>
-    <t>0.9504,0.0124,0.0042,0.0304</t>
-  </si>
-  <si>
-    <t>0.0234,0.0014,0.0019,0.9908</t>
-  </si>
-  <si>
-    <t>0.9961,0.0005,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9961,0.0007,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.9963,0.0012,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9974,0.0009,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9902,0.0055,0.0005,0.0023</t>
-  </si>
-  <si>
-    <t>0.9883,0.0073,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.8364,0.0082,0.2143,0.0012</t>
-  </si>
-  <si>
-    <t>0.2155,0.0016,0.8851,0.0010</t>
-  </si>
-  <si>
-    <t>0.4810,0.0160,0.6531,0.0005</t>
-  </si>
-  <si>
-    <t>0.0623,0.0028,0.9574,0.0006</t>
-  </si>
-  <si>
-    <t>0.9109,0.0046,0.1096,0.0007</t>
-  </si>
-  <si>
-    <t>0.0027,0.9918,0.0174,0.0003</t>
-  </si>
-  <si>
-    <t>0.0233,0.9697,0.0104,0.0005</t>
-  </si>
-  <si>
-    <t>0.2663,0.8220,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.0909,0.9266,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.0031,0.9940,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.3593,0.0017,0.7354,0.0057</t>
-  </si>
-  <si>
-    <t>0.5224,0.0350,0.5816,0.0111</t>
-  </si>
-  <si>
-    <t>0.0021,0.0011,0.9938,0.0072</t>
-  </si>
-  <si>
-    <t>0.0402,0.0414,0.9524,0.0070</t>
-  </si>
-  <si>
-    <t>0.1970,0.0107,0.9045,0.0011</t>
-  </si>
-  <si>
-    <t>0.0715,0.0021,0.9567,0.0018</t>
-  </si>
-  <si>
-    <t>0.0044,0.0013,0.9911,0.0038</t>
-  </si>
-  <si>
-    <t>0.6538,0.4143,0.0158,0.0014</t>
-  </si>
-  <si>
-    <t>0.3009,0.0693,0.6384,0.0051</t>
-  </si>
-  <si>
-    <t>0.0236,0.0149,0.9777,0.0071</t>
-  </si>
-  <si>
-    <t>0.0043,0.9761,0.0634,0.0003</t>
-  </si>
-  <si>
-    <t>0.6042,0.0128,0.5068,0.0021</t>
-  </si>
-  <si>
-    <t>0.8988,0.0232,0.0517,0.0116</t>
-  </si>
-  <si>
-    <t>0.8181,0.2716,0.0040,0.0020</t>
-  </si>
-  <si>
-    <t>0.0232,0.9591,0.0730,0.0009</t>
-  </si>
-  <si>
-    <t>0.0362,0.7230,0.2528,0.0850</t>
-  </si>
-  <si>
-    <t>0.0149,0.0008,0.8933,0.0606</t>
-  </si>
-  <si>
-    <t>0.0155,0.0260,0.9829,0.0012</t>
-  </si>
-  <si>
-    <t>0.0404,0.0039,0.9453,0.0160</t>
-  </si>
-  <si>
-    <t>0.0161,0.5470,0.9344,0.0034</t>
-  </si>
-  <si>
-    <t>0.0093,0.9608,0.0619,0.0006</t>
-  </si>
-  <si>
-    <t>0.0141,0.0114,0.9641,0.0048</t>
-  </si>
-  <si>
-    <t>0.1681,0.4839,0.1272,0.6970</t>
-  </si>
-  <si>
-    <t>0.0030,0.9721,0.0165,0.0840</t>
-  </si>
-  <si>
-    <t>0.0008,0.9954,0.0131,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.9974,0.0119,0.0085</t>
-  </si>
-  <si>
-    <t>0.0058,0.1157,0.9685,0.0076</t>
-  </si>
-  <si>
-    <t>0.0045,0.0725,0.9891,0.0010</t>
-  </si>
-  <si>
-    <t>0.0270,0.0020,0.9829,0.0008</t>
-  </si>
-  <si>
-    <t>0.0162,0.0007,0.9848,0.0012</t>
-  </si>
-  <si>
-    <t>0.0205,0.0034,0.9764,0.0042</t>
-  </si>
-  <si>
-    <t>0.0451,0.0422,0.9447,0.0049</t>
-  </si>
-  <si>
-    <t>0.9848,0.0170,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9775,0.0155,0.0046,0.0016</t>
-  </si>
-  <si>
-    <t>0.9837,0.0119,0.0006,0.0028</t>
-  </si>
-  <si>
-    <t>0.0894,0.0226,0.8733,0.0285</t>
-  </si>
-  <si>
-    <t>0.9884,0.0037,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.9855,0.0105,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.9430,0.0681,0.0073,0.0015</t>
-  </si>
-  <si>
-    <t>0.0065,0.9410,0.6362,0.0042</t>
-  </si>
-  <si>
-    <t>0.0013,0.4255,0.9925,0.0004</t>
-  </si>
-  <si>
-    <t>0.0095,0.0380,0.9038,0.0405</t>
-  </si>
-  <si>
-    <t>0.0002,0.9789,0.9816,0.0004</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9965,0.0007</t>
-  </si>
-  <si>
-    <t>0.0351,0.9576,0.0144,0.0007</t>
-  </si>
-  <si>
-    <t>0.0119,0.9909,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0005,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.9445,0.0071,0.0435,0.0039</t>
-  </si>
-  <si>
-    <t>0.0651,0.0061,0.8755,0.0007</t>
-  </si>
-  <si>
-    <t>0.0012,0.9484,0.9514,0.0008</t>
-  </si>
-  <si>
-    <t>0.0016,0.9805,0.6021,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.9967,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.9665,0.1899,0.0005</t>
-  </si>
-  <si>
-    <t>0.0039,0.0023,0.0807,0.9754</t>
-  </si>
-  <si>
-    <t>0.0141,0.0012,0.0005,0.9951</t>
-  </si>
-  <si>
-    <t>0.0013,0.0015,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0052,0.0092,0.0407,0.9764</t>
-  </si>
-  <si>
-    <t>0.0048,0.0007,0.0006,0.9971</t>
-  </si>
-  <si>
-    <t>0.0036,0.0009,0.0024,0.9964</t>
-  </si>
-  <si>
-    <t>0.0002,0.9907,0.9439,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.8471,0.9908,0.0002</t>
-  </si>
-  <si>
-    <t>0.0119,0.6682,0.7164,0.0173</t>
-  </si>
-  <si>
-    <t>0.0006,0.9692,0.9367,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.9817,0.7656,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9909,0.7592,0.0005</t>
-  </si>
-  <si>
-    <t>0.9921,0.0044,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9794,0.0377,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9893,0.0061,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0046,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9907,0.0051,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9931,0.0041,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9739,0.0299,0.0033,0.0016</t>
-  </si>
-  <si>
-    <t>0.9972,0.0010,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0008,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9956,0.0020,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9828,0.0181,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9969,0.0009,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9901,0.0036,0.0010,0.0025</t>
-  </si>
-  <si>
-    <t>0.0255,0.0014,0.9818,0.0015</t>
-  </si>
-  <si>
-    <t>0.0199,0.0081,0.9819,0.0031</t>
-  </si>
-  <si>
-    <t>0.8949,0.0010,0.0721,0.0110</t>
-  </si>
-  <si>
-    <t>0.2245,0.0018,0.8470,0.0038</t>
-  </si>
-  <si>
-    <t>0.0037,0.9887,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.0061,0.9909,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.3168,0.7905,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.0646,0.9532,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.0038,0.9927,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.0079,0.9924,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.6655,0.4714,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.2196,0.3285,0.2511,0.1064</t>
-  </si>
-  <si>
-    <t>0.7349,0.0021,0.4006,0.0016</t>
-  </si>
-  <si>
-    <t>0.4677,0.0329,0.4838,0.0655</t>
-  </si>
-  <si>
-    <t>0.8955,0.0036,0.1728,0.0003</t>
-  </si>
-  <si>
-    <t>0.0844,0.7690,0.4228,0.1917</t>
-  </si>
-  <si>
-    <t>0.0004,0.9971,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.0012,0.9957,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.9964,0.0008,0.0692</t>
-  </si>
-  <si>
-    <t>0.0005,0.9947,0.0848,0.0010</t>
-  </si>
-  <si>
-    <t>0.0051,0.9923,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.6791,0.3554,0.0205,0.0014</t>
-  </si>
-  <si>
-    <t>0.9627,0.0279,0.0060,0.0009</t>
-  </si>
-  <si>
-    <t>0.9909,0.0025,0.0013,0.0019</t>
-  </si>
-  <si>
-    <t>0.9923,0.0030,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9967,0.0005,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9760,0.0045,0.0103,0.0036</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9734,0.0134,0.0039,0.0035</t>
-  </si>
-  <si>
-    <t>0.9846,0.0078,0.0030,0.0011</t>
-  </si>
-  <si>
-    <t>0.0186,0.5164,0.6345,0.0203</t>
-  </si>
-  <si>
-    <t>0.0087,0.5109,0.9193,0.0006</t>
-  </si>
-  <si>
-    <t>0.0355,0.0328,0.9705,0.0002</t>
-  </si>
-  <si>
-    <t>0.1864,0.2963,0.6686,0.0071</t>
-  </si>
-  <si>
-    <t>0.9865,0.0043,0.0025,0.0014</t>
-  </si>
-  <si>
-    <t>0.8146,0.0048,0.0799,0.0571</t>
-  </si>
-  <si>
-    <t>0.7037,0.0003,0.5807,0.0005</t>
-  </si>
-  <si>
-    <t>0.6864,0.0228,0.4578,0.0051</t>
-  </si>
-  <si>
-    <t>0.1017,0.0018,0.0049,0.9490</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0009,0.9991</t>
-  </si>
-  <si>
-    <t>0.0021,0.0400,0.0006,0.9965</t>
-  </si>
-  <si>
-    <t>0.0032,0.0002,0.0029,0.9968</t>
-  </si>
-  <si>
-    <t>0.0009,0.9482,0.7095,0.0030</t>
-  </si>
-  <si>
-    <t>0.9885,0.0064,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.0238,0.9626,0.0057,0.0067</t>
-  </si>
-  <si>
-    <t>0.9868,0.0031,0.0021,0.0031</t>
-  </si>
-  <si>
-    <t>0.2282,0.8004,0.0101,0.0132</t>
-  </si>
-  <si>
-    <t>0.9892,0.0018,0.0015,0.0034</t>
-  </si>
-  <si>
-    <t>0.7452,0.0008,0.0054,0.3926</t>
-  </si>
-  <si>
-    <t>0.9937,0.0007,0.0003,0.0025</t>
-  </si>
-  <si>
-    <t>0.0980,0.0329,0.5754,0.3540</t>
-  </si>
-  <si>
-    <t>0.7533,0.0010,0.0006,0.5313</t>
-  </si>
-  <si>
-    <t>0.7318,0.0032,0.0034,0.4206</t>
-  </si>
-  <si>
-    <t>0.7388,0.2878,0.0176,0.0044</t>
-  </si>
-  <si>
-    <t>0.9767,0.0051,0.0115,0.0009</t>
-  </si>
-  <si>
-    <t>0.9846,0.0071,0.0029,0.0010</t>
-  </si>
-  <si>
-    <t>0.0569,0.7428,0.1690,0.0233</t>
-  </si>
-  <si>
-    <t>0.9803,0.0194,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9430,0.0402,0.0123,0.0032</t>
-  </si>
-  <si>
-    <t>0.9952,0.0015,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9792,0.0032,0.0012,0.0111</t>
-  </si>
-  <si>
-    <t>0.9944,0.0011,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9964,0.0005,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9917,0.0031,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.9836,0.0068,0.0023,0.0037</t>
-  </si>
-  <si>
-    <t>0.9883,0.0013,0.0007,0.0070</t>
-  </si>
-  <si>
-    <t>0.9919,0.0011,0.0008,0.0024</t>
-  </si>
-  <si>
-    <t>0.9303,0.1161,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.7192,0.3476,0.0119,0.0049</t>
-  </si>
-  <si>
-    <t>0.4499,0.7116,0.0046,0.0017</t>
-  </si>
-  <si>
-    <t>0.7042,0.1444,0.1362,0.0592</t>
-  </si>
-  <si>
-    <t>0.9925,0.0031,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9270,0.0342,0.0243,0.0091</t>
-  </si>
-  <si>
-    <t>0.9883,0.0047,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.7539,0.2682,0.0186,0.0039</t>
-  </si>
-  <si>
-    <t>0.0040,0.0120,0.9949,0.0008</t>
-  </si>
-  <si>
-    <t>0.9873,0.0072,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.0048,0.0012,0.9938,0.0010</t>
-  </si>
-  <si>
-    <t>0.0021,0.0352,0.9928,0.0016</t>
-  </si>
-  <si>
-    <t>0.0695,0.0023,0.9603,0.0008</t>
-  </si>
-  <si>
-    <t>0.0044,0.0178,0.9945,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.0389,0.9943,0.0011</t>
-  </si>
-  <si>
-    <t>0.0049,0.0005,0.9950,0.0005</t>
-  </si>
-  <si>
-    <t>0.0067,0.0025,0.9918,0.0018</t>
-  </si>
-  <si>
-    <t>0.0547,0.0021,0.9686,0.0011</t>
-  </si>
-  <si>
-    <t>0.3411,0.0064,0.8200,0.0010</t>
-  </si>
-  <si>
-    <t>0.8173,0.0405,0.1507,0.0047</t>
-  </si>
-  <si>
-    <t>0.4798,0.0090,0.7017,0.0009</t>
-  </si>
-  <si>
-    <t>0.3422,0.2197,0.2998,0.0013</t>
-  </si>
-  <si>
-    <t>0.1766,0.0998,0.7891,0.0041</t>
-  </si>
-  <si>
-    <t>0.5713,0.1375,0.3441,0.0717</t>
-  </si>
-  <si>
-    <t>0.6094,0.0356,0.4139,0.0165</t>
-  </si>
-  <si>
-    <t>0.5138,0.7042,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9481,0.1159,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9773,0.0511,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9840,0.0215,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.7073,0.4517,0.0066,0.0010</t>
-  </si>
-  <si>
-    <t>0.6273,0.0213,0.4914,0.0056</t>
-  </si>
-  <si>
-    <t>0.9897,0.0003,0.0109,0.0003</t>
-  </si>
-  <si>
-    <t>0.9409,0.0078,0.0423,0.0110</t>
-  </si>
-  <si>
-    <t>0.5145,0.0300,0.5180,0.0153</t>
-  </si>
-  <si>
-    <t>0.9648,0.0068,0.0109,0.0093</t>
-  </si>
-  <si>
-    <t>0.0240,0.0304,0.9403,0.0092</t>
-  </si>
-  <si>
-    <t>0.0662,0.0158,0.9473,0.0054</t>
-  </si>
-  <si>
-    <t>0.0220,0.0166,0.9827,0.0039</t>
-  </si>
-  <si>
-    <t>0.0089,0.0539,0.9078,0.0086</t>
-  </si>
-  <si>
-    <t>0.0049,0.0061,0.9843,0.0034</t>
-  </si>
-  <si>
-    <t>0.9943,0.0014,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9861,0.0023,0.0052,0.0013</t>
-  </si>
-  <si>
-    <t>0.9762,0.0298,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9939,0.0038,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9922,0.0043,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9963,0.0013,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9721,0.0103,0.0102,0.0040</t>
-  </si>
-  <si>
-    <t>0.9955,0.0010,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.0096,0.0070,0.9862,0.0043</t>
-  </si>
-  <si>
-    <t>0.0761,0.0880,0.7605,0.0034</t>
-  </si>
-  <si>
-    <t>0.8479,0.0153,0.1074,0.0190</t>
-  </si>
-  <si>
-    <t>0.0026,0.0009,0.9956,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0023,0.9951,0.0059</t>
-  </si>
-  <si>
-    <t>0.0673,0.1393,0.6608,0.0027</t>
-  </si>
-  <si>
-    <t>0.0020,0.0003,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0345,0.0028,0.9678,0.0012</t>
-  </si>
-  <si>
-    <t>0.0036,0.0030,0.9926,0.0019</t>
-  </si>
-  <si>
-    <t>0.0079,0.0401,0.9843,0.0006</t>
-  </si>
-  <si>
-    <t>0.0285,0.0413,0.9433,0.0021</t>
-  </si>
-  <si>
-    <t>0.9271,0.0021,0.0840,0.0034</t>
-  </si>
-  <si>
-    <t>0.4311,0.0007,0.7476,0.0008</t>
-  </si>
-  <si>
-    <t>0.8236,0.0018,0.1263,0.0204</t>
-  </si>
-  <si>
-    <t>0.9941,0.0049,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9930,0.0081,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9938,0.0050,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9902,0.0094,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9937,0.0006,0.0005,0.0022</t>
-  </si>
-  <si>
-    <t>0.9911,0.0032,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0017,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9925,0.0024,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.0641,0.0280,0.9029,0.0112</t>
-  </si>
-  <si>
-    <t>0.0049,0.0117,0.9922,0.0005</t>
-  </si>
-  <si>
-    <t>0.0035,0.0456,0.9817,0.0015</t>
-  </si>
-  <si>
-    <t>0.0201,0.0372,0.9504,0.0010</t>
-  </si>
-  <si>
-    <t>0.0049,0.0013,0.9921,0.0013</t>
-  </si>
-  <si>
-    <t>0.0038,0.0139,0.9410,0.1098</t>
-  </si>
-  <si>
-    <t>0.0227,0.0230,0.9677,0.0022</t>
-  </si>
-  <si>
-    <t>0.0298,0.0238,0.9350,0.0397</t>
-  </si>
-  <si>
-    <t>0.7584,0.0005,0.0006,0.5055</t>
-  </si>
-  <si>
-    <t>0.0510,0.0261,0.0008,0.9802</t>
-  </si>
-  <si>
-    <t>0.1920,0.0044,0.0012,0.9305</t>
-  </si>
-  <si>
-    <t>0.0087,0.0001,0.0006,0.9961</t>
-  </si>
-  <si>
-    <t>0.0224,0.0001,0.0001,0.9963</t>
-  </si>
-  <si>
-    <t>0.9496,0.0088,0.0265,0.0063</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8073,0.0564,0.0198,0.1201</t>
+  </si>
+  <si>
+    <t>0.0876,0.0007,0.0003,0.9800</t>
+  </si>
+  <si>
+    <t>0.9136,0.0031,0.0028,0.0798</t>
+  </si>
+  <si>
+    <t>0.0143,0.0001,0.0018,0.9936</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9927,0.0038,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9882,0.0072,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9974,0.0012,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0046,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9135,0.0160,0.0614,0.0022</t>
+  </si>
+  <si>
+    <t>0.0198,0.0013,0.9601,0.0244</t>
+  </si>
+  <si>
+    <t>0.6095,0.0031,0.7088,0.0002</t>
+  </si>
+  <si>
+    <t>0.0139,0.0020,0.9850,0.0005</t>
+  </si>
+  <si>
+    <t>0.8170,0.0089,0.1847,0.0087</t>
+  </si>
+  <si>
+    <t>0.0073,0.9913,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0095,0.9864,0.0087,0.0003</t>
+  </si>
+  <si>
+    <t>0.0910,0.9389,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.0484,0.9453,0.0074,0.0022</t>
+  </si>
+  <si>
+    <t>0.0081,0.9856,0.0088,0.0018</t>
+  </si>
+  <si>
+    <t>0.9004,0.0074,0.0935,0.0041</t>
+  </si>
+  <si>
+    <t>0.4667,0.0116,0.6752,0.0042</t>
+  </si>
+  <si>
+    <t>0.0052,0.0112,0.9942,0.0012</t>
+  </si>
+  <si>
+    <t>0.2908,0.0072,0.8189,0.0028</t>
+  </si>
+  <si>
+    <t>0.1940,0.0041,0.9252,0.0007</t>
+  </si>
+  <si>
+    <t>0.0851,0.0008,0.9561,0.0009</t>
+  </si>
+  <si>
+    <t>0.0094,0.0039,0.9864,0.0031</t>
+  </si>
+  <si>
+    <t>0.6390,0.4034,0.0167,0.0007</t>
+  </si>
+  <si>
+    <t>0.2388,0.7537,0.0163,0.0031</t>
+  </si>
+  <si>
+    <t>0.0064,0.0074,0.9838,0.0228</t>
+  </si>
+  <si>
+    <t>0.0003,0.9966,0.0146,0.0001</t>
+  </si>
+  <si>
+    <t>0.8396,0.0259,0.0846,0.0223</t>
+  </si>
+  <si>
+    <t>0.9739,0.0083,0.0057,0.0045</t>
+  </si>
+  <si>
+    <t>0.9049,0.1138,0.0070,0.0015</t>
+  </si>
+  <si>
+    <t>0.0834,0.9289,0.0064,0.0003</t>
+  </si>
+  <si>
+    <t>0.0134,0.9631,0.0039,0.0330</t>
+  </si>
+  <si>
+    <t>0.0934,0.0170,0.9359,0.0103</t>
+  </si>
+  <si>
+    <t>0.1296,0.0099,0.9195,0.0036</t>
+  </si>
+  <si>
+    <t>0.0521,0.0004,0.9407,0.0050</t>
+  </si>
+  <si>
+    <t>0.0068,0.0746,0.9859,0.0013</t>
+  </si>
+  <si>
+    <t>0.0061,0.8584,0.1838,0.0013</t>
+  </si>
+  <si>
+    <t>0.0644,0.0033,0.9550,0.0007</t>
+  </si>
+  <si>
+    <t>0.1391,0.5001,0.0882,0.6972</t>
+  </si>
+  <si>
+    <t>0.0016,0.9849,0.0012,0.0496</t>
+  </si>
+  <si>
+    <t>0.0007,0.9954,0.0110,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.9947,0.0145,0.0049</t>
+  </si>
+  <si>
+    <t>0.0043,0.2541,0.8425,0.0192</t>
+  </si>
+  <si>
+    <t>0.0021,0.0446,0.9943,0.0010</t>
+  </si>
+  <si>
+    <t>0.0660,0.0075,0.9520,0.0018</t>
+  </si>
+  <si>
+    <t>0.0097,0.0019,0.9888,0.0024</t>
+  </si>
+  <si>
+    <t>0.0166,0.0058,0.9769,0.0040</t>
+  </si>
+  <si>
+    <t>0.0070,0.0088,0.9860,0.0025</t>
+  </si>
+  <si>
+    <t>0.9891,0.0129,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9808,0.0063,0.0100,0.0005</t>
+  </si>
+  <si>
+    <t>0.9821,0.0127,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.0118,0.0351,0.9823,0.0073</t>
+  </si>
+  <si>
+    <t>0.9918,0.0026,0.0025,0.0005</t>
+  </si>
+  <si>
+    <t>0.9892,0.0039,0.0045,0.0003</t>
+  </si>
+  <si>
+    <t>0.9867,0.0058,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.0005,0.9842,0.9262,0.0011</t>
+  </si>
+  <si>
+    <t>0.0100,0.0749,0.9639,0.0033</t>
+  </si>
+  <si>
+    <t>0.0035,0.4071,0.9721,0.0057</t>
+  </si>
+  <si>
+    <t>0.0011,0.9722,0.9020,0.0020</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9975,0.0013</t>
+  </si>
+  <si>
+    <t>0.0124,0.9865,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9989,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9765,0.0027,0.0192,0.0013</t>
+  </si>
+  <si>
+    <t>0.2281,0.0889,0.7764,0.0068</t>
+  </si>
+  <si>
+    <t>0.0690,0.0055,0.9369,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.9098,0.9095,0.0015</t>
+  </si>
+  <si>
+    <t>0.0031,0.9680,0.5230,0.0012</t>
+  </si>
+  <si>
+    <t>0.0029,0.9894,0.0105,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.9798,0.3067,0.0008</t>
+  </si>
+  <si>
+    <t>0.0052,0.0006,0.1123,0.9642</t>
+  </si>
+  <si>
+    <t>0.0064,0.0065,0.0009,0.9961</t>
+  </si>
+  <si>
+    <t>0.0058,0.0005,0.0003,0.9973</t>
+  </si>
+  <si>
+    <t>0.0087,0.0028,0.0032,0.9922</t>
+  </si>
+  <si>
+    <t>0.0039,0.0003,0.0013,0.9962</t>
+  </si>
+  <si>
+    <t>0.0041,0.0119,0.0017,0.9949</t>
+  </si>
+  <si>
+    <t>0.0009,0.9735,0.9204,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.9176,0.9912,0.0002</t>
+  </si>
+  <si>
+    <t>0.0082,0.3817,0.8092,0.0055</t>
+  </si>
+  <si>
+    <t>0.0019,0.9688,0.7442,0.0018</t>
+  </si>
+  <si>
+    <t>0.0004,0.9922,0.2198,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9939,0.8860,0.0006</t>
+  </si>
+  <si>
+    <t>0.9968,0.0013,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9801,0.0195,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.9912,0.0124,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9863,0.0087,0.0026,0.0014</t>
+  </si>
+  <si>
+    <t>0.9981,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0134,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9885,0.0078,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9879,0.0044,0.0017,0.0021</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9891,0.0100,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9941,0.0032,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.0066,0.0024,0.9911,0.0045</t>
+  </si>
+  <si>
+    <t>0.1629,0.0231,0.8618,0.0073</t>
+  </si>
+  <si>
+    <t>0.8033,0.0023,0.1855,0.0190</t>
+  </si>
+  <si>
+    <t>0.0089,0.0012,0.9821,0.0079</t>
+  </si>
+  <si>
+    <t>0.0529,0.9679,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0464,0.9501,0.0030,0.0039</t>
+  </si>
+  <si>
+    <t>0.0925,0.9225,0.0063,0.0015</t>
+  </si>
+  <si>
+    <t>0.0415,0.9595,0.0053,0.0016</t>
+  </si>
+  <si>
+    <t>0.0242,0.9789,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.8861,0.1867,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.5835,0.2127,0.1861,0.0176</t>
+  </si>
+  <si>
+    <t>0.0388,0.0016,0.9684,0.0033</t>
+  </si>
+  <si>
+    <t>0.8553,0.0489,0.0576,0.0038</t>
+  </si>
+  <si>
+    <t>0.8283,0.0042,0.2642,0.0010</t>
+  </si>
+  <si>
+    <t>0.2180,0.1430,0.7650,0.1501</t>
+  </si>
+  <si>
+    <t>0.0036,0.9873,0.0112,0.0024</t>
+  </si>
+  <si>
+    <t>0.0016,0.9949,0.0163,0.0011</t>
+  </si>
+  <si>
+    <t>0.0012,0.9956,0.0011,0.0032</t>
+  </si>
+  <si>
+    <t>0.0007,0.9974,0.0120,0.0003</t>
+  </si>
+  <si>
+    <t>0.0145,0.9815,0.0160,0.0002</t>
+  </si>
+  <si>
+    <t>0.7584,0.1883,0.0629,0.0034</t>
+  </si>
+  <si>
+    <t>0.9618,0.0242,0.0091,0.0005</t>
+  </si>
+  <si>
+    <t>0.9794,0.0087,0.0060,0.0029</t>
+  </si>
+  <si>
+    <t>0.9954,0.0012,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9914,0.0034,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9747,0.0067,0.0097,0.0021</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9909,0.0026,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9869,0.0015,0.0065,0.0007</t>
+  </si>
+  <si>
+    <t>0.0016,0.9574,0.5469,0.0026</t>
+  </si>
+  <si>
+    <t>0.0143,0.1650,0.9296,0.0007</t>
+  </si>
+  <si>
+    <t>0.0069,0.0182,0.9893,0.0009</t>
+  </si>
+  <si>
+    <t>0.1055,0.0475,0.9322,0.0011</t>
+  </si>
+  <si>
+    <t>0.9813,0.0023,0.0119,0.0002</t>
+  </si>
+  <si>
+    <t>0.6049,0.0315,0.4597,0.0245</t>
+  </si>
+  <si>
+    <t>0.1809,0.0006,0.8828,0.0029</t>
+  </si>
+  <si>
+    <t>0.8439,0.0223,0.1629,0.0032</t>
+  </si>
+  <si>
+    <t>0.0909,0.0013,0.0045,0.9547</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0008,0.9996</t>
+  </si>
+  <si>
+    <t>0.0048,0.0030,0.0011,0.9964</t>
+  </si>
+  <si>
+    <t>0.0053,0.0001,0.0002,0.9982</t>
+  </si>
+  <si>
+    <t>0.0008,0.9733,0.6174,0.0027</t>
+  </si>
+  <si>
+    <t>0.9856,0.0093,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.0341,0.9535,0.0015,0.0140</t>
+  </si>
+  <si>
+    <t>0.9815,0.0022,0.0035,0.0053</t>
+  </si>
+  <si>
+    <t>0.0887,0.9082,0.0066,0.0230</t>
+  </si>
+  <si>
+    <t>0.9916,0.0003,0.0017,0.0025</t>
+  </si>
+  <si>
+    <t>0.1350,0.0028,0.0017,0.9552</t>
+  </si>
+  <si>
+    <t>0.9857,0.0004,0.0002,0.0143</t>
+  </si>
+  <si>
+    <t>0.0567,0.3204,0.5123,0.1176</t>
+  </si>
+  <si>
+    <t>0.1879,0.0007,0.0019,0.9368</t>
+  </si>
+  <si>
+    <t>0.4101,0.0130,0.0157,0.7629</t>
+  </si>
+  <si>
+    <t>0.7364,0.3170,0.0081,0.0015</t>
+  </si>
+  <si>
+    <t>0.9829,0.0050,0.0062,0.0006</t>
+  </si>
+  <si>
+    <t>0.9818,0.0069,0.0034,0.0012</t>
+  </si>
+  <si>
+    <t>0.1024,0.6948,0.1835,0.0173</t>
+  </si>
+  <si>
+    <t>0.9871,0.0029,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.9620,0.0189,0.0121,0.0015</t>
+  </si>
+  <si>
+    <t>0.9766,0.0104,0.0023,0.0086</t>
+  </si>
+  <si>
+    <t>0.9939,0.0016,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9941,0.0007,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9910,0.0009,0.0009,0.0039</t>
+  </si>
+  <si>
+    <t>0.9932,0.0022,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9760,0.0136,0.0027,0.0066</t>
+  </si>
+  <si>
+    <t>0.9935,0.0010,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9949,0.0021,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9303,0.1113,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.3611,0.6811,0.0088,0.0066</t>
+  </si>
+  <si>
+    <t>0.7271,0.3782,0.0071,0.0022</t>
+  </si>
+  <si>
+    <t>0.3177,0.6399,0.1624,0.0237</t>
+  </si>
+  <si>
+    <t>0.9812,0.0084,0.0058,0.0017</t>
+  </si>
+  <si>
+    <t>0.9043,0.0344,0.0681,0.0020</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9581,0.0611,0.0028,0.0013</t>
+  </si>
+  <si>
+    <t>0.0094,0.0293,0.9865,0.0007</t>
+  </si>
+  <si>
+    <t>0.9875,0.0048,0.0031,0.0013</t>
+  </si>
+  <si>
+    <t>0.0118,0.0039,0.9920,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0202,0.9649,0.0476</t>
+  </si>
+  <si>
+    <t>0.0040,0.0026,0.9934,0.0008</t>
+  </si>
+  <si>
+    <t>0.0100,0.0356,0.9878,0.0014</t>
+  </si>
+  <si>
+    <t>0.0022,0.1563,0.9902,0.0004</t>
+  </si>
+  <si>
+    <t>0.0033,0.0017,0.9958,0.0004</t>
+  </si>
+  <si>
+    <t>0.0068,0.0034,0.9943,0.0006</t>
+  </si>
+  <si>
+    <t>0.0885,0.0047,0.9391,0.0024</t>
+  </si>
+  <si>
+    <t>0.1183,0.0196,0.8788,0.0375</t>
+  </si>
+  <si>
+    <t>0.7096,0.0886,0.2712,0.0132</t>
+  </si>
+  <si>
+    <t>0.3594,0.0205,0.7327,0.0017</t>
+  </si>
+  <si>
+    <t>0.0954,0.6422,0.2859,0.0081</t>
+  </si>
+  <si>
+    <t>0.4988,0.0784,0.4776,0.0061</t>
+  </si>
+  <si>
+    <t>0.5394,0.0186,0.5465,0.0079</t>
+  </si>
+  <si>
+    <t>0.5693,0.0659,0.4504,0.0074</t>
+  </si>
+  <si>
+    <t>0.1359,0.9088,0.0013,0.0021</t>
+  </si>
+  <si>
+    <t>0.1173,0.9306,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9537,0.0967,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9882,0.0082,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.4544,0.6717,0.0045,0.0019</t>
+  </si>
+  <si>
+    <t>0.3836,0.4807,0.1380,0.0411</t>
+  </si>
+  <si>
+    <t>0.9711,0.0006,0.0412,0.0010</t>
+  </si>
+  <si>
+    <t>0.9669,0.0046,0.0078,0.0087</t>
+  </si>
+  <si>
+    <t>0.9346,0.0019,0.1063,0.0014</t>
+  </si>
+  <si>
+    <t>0.8857,0.0117,0.0887,0.0229</t>
+  </si>
+  <si>
+    <t>0.0062,0.0166,0.9787,0.0117</t>
+  </si>
+  <si>
+    <t>0.0314,0.1417,0.9209,0.0286</t>
+  </si>
+  <si>
+    <t>0.0074,0.0064,0.9925,0.0020</t>
+  </si>
+  <si>
+    <t>0.0856,0.0091,0.9630,0.0007</t>
+  </si>
+  <si>
+    <t>0.0026,0.0729,0.9447,0.0028</t>
+  </si>
+  <si>
+    <t>0.9892,0.0045,0.0010,0.0023</t>
+  </si>
+  <si>
+    <t>0.9878,0.0014,0.0061,0.0014</t>
+  </si>
+  <si>
+    <t>0.9740,0.0236,0.0049,0.0012</t>
+  </si>
+  <si>
+    <t>0.9947,0.0057,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0133,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0015,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9671,0.0110,0.0051,0.0103</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0175,0.0130,0.9776,0.0018</t>
+  </si>
+  <si>
+    <t>0.0238,0.9306,0.0802,0.0029</t>
+  </si>
+  <si>
+    <t>0.7128,0.0332,0.1628,0.0393</t>
+  </si>
+  <si>
+    <t>0.0016,0.0046,0.9963,0.0014</t>
+  </si>
+  <si>
+    <t>0.0010,0.0016,0.9927,0.0088</t>
+  </si>
+  <si>
+    <t>0.0048,0.0728,0.9899,0.0008</t>
+  </si>
+  <si>
+    <t>0.0013,0.0546,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.5100,0.0040,0.6287,0.0007</t>
+  </si>
+  <si>
+    <t>0.0056,0.0010,0.9930,0.0008</t>
+  </si>
+  <si>
+    <t>0.0025,0.0040,0.9939,0.0002</t>
+  </si>
+  <si>
+    <t>0.0793,0.0508,0.8200,0.0867</t>
+  </si>
+  <si>
+    <t>0.9148,0.0020,0.1511,0.0005</t>
+  </si>
+  <si>
+    <t>0.8445,0.0018,0.2405,0.0023</t>
+  </si>
+  <si>
+    <t>0.9615,0.0006,0.0193,0.0057</t>
+  </si>
+  <si>
+    <t>0.9869,0.0127,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0044,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0076,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9921,0.0094,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9934,0.0029,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9933,0.0028,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0046,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0027,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0267,0.0206,0.9414,0.0053</t>
+  </si>
+  <si>
+    <t>0.0038,0.0927,0.9879,0.0005</t>
+  </si>
+  <si>
+    <t>0.0290,0.0086,0.9689,0.0014</t>
+  </si>
+  <si>
+    <t>0.0999,0.0052,0.9265,0.0018</t>
+  </si>
+  <si>
+    <t>0.0025,0.0006,0.9950,0.0011</t>
+  </si>
+  <si>
+    <t>0.0255,0.0190,0.9428,0.0543</t>
+  </si>
+  <si>
+    <t>0.7891,0.0067,0.2733,0.0034</t>
+  </si>
+  <si>
+    <t>0.0082,0.0059,0.9721,0.0210</t>
+  </si>
+  <si>
+    <t>0.6841,0.0016,0.0025,0.5084</t>
+  </si>
+  <si>
+    <t>0.0133,0.0073,0.0025,0.9923</t>
+  </si>
+  <si>
+    <t>0.0326,0.0006,0.0004,0.9920</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0196,0.0001,0.0002,0.9958</t>
+  </si>
+  <si>
+    <t>0.8274,0.0321,0.0346,0.1201</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2427,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,10 +4149,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5129,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5423,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
